--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:27</t>
+    <t xml:space="preserve">2026-09-10 01:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:42</t>
+    <t xml:space="preserve">2026-09-18 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:38</t>
+    <t xml:space="preserve">2026-09-23 15:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernandez</t>
+    <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:44</t>
+    <t xml:space="preserve">2026-10-04 10:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:50</t>
+    <t xml:space="preserve">2026-10-05 16:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -837,7 +837,7 @@
         <v>64.39</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>93.78</v>
+        <v>93.79</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>87.99</v>
@@ -1487,7 +1487,7 @@
         <v>100.22</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>110.39</v>
+        <v>110.4</v>
       </c>
       <c r="I33" s="2" t="n">
         <v>62.71</v>
